--- a/toolkit/study-sponsor-charter.xlsx
+++ b/toolkit/study-sponsor-charter.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charter" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Charter" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -568,6 +568,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -580,6 +581,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -671,6 +673,7 @@
       <c r="C15" s="9" t="n"/>
       <c r="D15" s="10" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
@@ -773,52 +776,54 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
+          <t>Key supplier(s)</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
           <t>Total days freed</t>
         </is>
       </c>
-      <c r="C26" s="12">
-        <f>SUM(C19:C25)</f>
+      <c r="C27" s="12">
+        <f>SUM(C19:C26)</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>What the sponsor commits to</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Commitment</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Agreed (Y/N)</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Open the kick-off and say why this study matters</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Protect the team's time for the whole workshop</t>
+          <t>Open the kick-off and say why this study matters</t>
         </is>
       </c>
       <c r="B31" s="8" t="n"/>
@@ -827,7 +832,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Decide at the decision meeting, and sign the decision log there</t>
+          <t>Protect the team's time for the whole workshop</t>
         </is>
       </c>
       <c r="B32" s="8" t="n"/>
@@ -836,87 +841,88 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>Fund the engineering time to put approved ideas into production</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>£ or hours:</t>
-        </is>
-      </c>
+          <t>Decide at the decision meeting, and sign the decision log there</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Clear blockers within a week of hearing about them</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="n"/>
+          <t>Fund the engineering time to put approved ideas into production</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>£ or hours:</t>
+        </is>
+      </c>
       <c r="C34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
+          <t>Clear blockers within a week of hearing about them</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
           <t>Chair a 30-minute funnel review every month until the savings are in production</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>First review:</t>
         </is>
       </c>
-      <c r="C35" s="8" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="C36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Commitments agreed</t>
         </is>
       </c>
-      <c r="C36" s="13">
-        <f>COUNTIF(C30:C35,"Y")&amp;" of 6"</f>
+      <c r="C37" s="13">
+        <f>COUNTIF(C31:C36,"Y")&amp;" of 6"</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Key dates</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>Information pack ready</t>
-        </is>
-      </c>
-      <c r="B40" s="14" t="n"/>
-      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Information pack ready</t>
         </is>
       </c>
       <c r="B41" s="14" t="n"/>
@@ -925,7 +931,7 @@
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>Decision meeting</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="B42" s="14" t="n"/>
@@ -934,7 +940,7 @@
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>First monthly review</t>
+          <t>Decision meeting</t>
         </is>
       </c>
       <c r="B43" s="14" t="n"/>
@@ -943,14 +949,24 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>Savings checked at L4 (target date)</t>
+          <t>First monthly review</t>
         </is>
       </c>
       <c r="B44" s="14" t="n"/>
       <c r="C44" s="8" t="n"/>
     </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>Savings checked at L4 (target date)</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="n"/>
+      <c r="C45" s="8" t="n"/>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>© Avinash Bhosale · VAVEhub Toolkit — free for personal &amp; internal company use with attribution; commercial redistribution or resale prohibited</t>
         </is>
@@ -958,17 +974,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
